--- a/02-three-statement-model/Three_Statement_Model.xlsx
+++ b/02-three-statement-model/Three_Statement_Model.xlsx
@@ -245,7 +245,7 @@
     <t xml:space="preserve">Capex (% du CA)</t>
   </si>
   <si>
-    <t xml:space="preserve">Hypothèse personnelle. Pour comparaison, le capex réel publié s'est établi entre 122 et 176 M€ selon les exercices et la base (brut/net de cessions) - voir Sources ; l'hypothèse se situe dans cet ordre de grandeur.</t>
+    <t xml:space="preserve">Hypothèse personnelle. Pour comparaison, le capex réel publié s'est établi entre 122 et 176 M€ selon les exercices et la base (brut/net de cessions), voir Sources ; l'hypothèse se situe dans cet ordre de grandeur.</t>
   </si>
   <si>
     <t xml:space="preserve">Délai clients (jours de CA)</t>
@@ -332,7 +332,7 @@
     <t xml:space="preserve">Dette nette hors IFRS16 (négatif = position de cash net)</t>
   </si>
   <si>
-    <t xml:space="preserve">958 - 1 104 = -146 M€ : Fnac Darty est en position de cash net hors IFRS16 à fin FY2025, et non en dette nette - point clarifié par cette recherche (un résidu ambigu sur ce point avait été signalé dans le projet 4 Transaction Services DD).</t>
+    <t xml:space="preserve">958 - 1 104 = -146 M€ : Fnac Darty est en position de cash net hors IFRS16 à fin FY2025, et non en dette nette. Point clarifié par cette recherche (un résidu ambigu sur ce point avait été signalé dans le projet 4 Transaction Services DD).</t>
   </si>
   <si>
     <t xml:space="preserve">EBITDA FY2025A réel</t>
@@ -758,7 +758,7 @@
     <t xml:space="preserve">VE réelle actuelle / EBITDA FY2025A réel, y compris IFRS16</t>
   </si>
   <si>
-    <t xml:space="preserve">Lecture : le multiple implicite du DCF et le multiple réel (y compris IFRS16) sont proches - voir Checks.</t>
+    <t xml:space="preserve">Lecture : le multiple implicite du DCF et le multiple réel (y compris IFRS16) sont proches ; voir Checks.</t>
   </si>
   <si>
     <t xml:space="preserve">Note méthodologique IFRS16 : sur les 5 années explicites, le D&amp;A modélisé (4,5 % du CA, cohérent avec le réel FY2025A qui inclut l'amortissement des droits d'usage IFRS16) dépasse le capex (2,5 % du CA, proche du capex réel publié) - un écart réel pour un réseau mature, pas une erreur. Pour éviter de prolonger cet écart à l'infini dans la valeur terminale, le FCFF terminal (ligne 22) est normalisé : capex terminal = D&amp;A terminal (régime stationnaire), convention standard pour une perpétuité - voir PP&amp;E Schedule.</t>
@@ -1003,7 +1003,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE7F2FF"/>
-        <bgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFE2F0D9"/>
       </patternFill>
     </fill>
     <fill>
@@ -1068,131 +1068,131 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="171" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="172" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1205,6 +1205,36 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <charset val="1"/>
+        <family val="0"/>
+        <b val="1"/>
+        <color rgb="FF2E7D32"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE2F0D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <charset val="1"/>
+        <family val="0"/>
+        <b val="1"/>
+        <color rgb="FFC62828"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFCE4E4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -1225,7 +1255,7 @@
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFFFCC"/>
+      <rgbColor rgb="FFFCE4E4"/>
       <rgbColor rgb="FFE7F2FF"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
@@ -1241,7 +1271,7 @@
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
       <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFE2F0D9"/>
       <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FFB3B3B3"/>
       <rgbColor rgb="FFFF99CC"/>
@@ -1256,10 +1286,10 @@
       <rgbColor rgb="FF7F7F7F"/>
       <rgbColor rgb="FFA5A5A5"/>
       <rgbColor rgb="FF1F3864"/>
-      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF2E7D32"/>
       <rgbColor rgb="FF003300"/>
       <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FFC62828"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF333333"/>
@@ -1434,8 +1464,8 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="90438293"/>
-        <c:axId val="67770898"/>
+        <c:axId val="25065761"/>
+        <c:axId val="36746533"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -1708,11 +1738,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="50077080"/>
-        <c:axId val="53042376"/>
+        <c:axId val="97582126"/>
+        <c:axId val="29730322"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="90438293"/>
+        <c:axId val="25065761"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1743,7 +1773,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="67770898"/>
+        <c:crossAx val="36746533"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1751,7 +1781,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="67770898"/>
+        <c:axId val="36746533"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1825,12 +1855,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="90438293"/>
+        <c:crossAx val="25065761"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="50077080"/>
+        <c:axId val="97582126"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1861,7 +1891,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="53042376"/>
+        <c:crossAx val="29730322"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1869,7 +1899,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="53042376"/>
+        <c:axId val="29730322"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1934,7 +1964,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="50077080"/>
+        <c:crossAx val="97582126"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2312,8 +2342,8 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="51026761"/>
-        <c:axId val="37374148"/>
+        <c:axId val="85334945"/>
+        <c:axId val="18096949"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="stacked"/>
@@ -2438,11 +2468,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="42232629"/>
-        <c:axId val="65201230"/>
+        <c:axId val="58969142"/>
+        <c:axId val="97377216"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="51026761"/>
+        <c:axId val="85334945"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2473,7 +2503,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="37374148"/>
+        <c:crossAx val="18096949"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2481,7 +2511,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="37374148"/>
+        <c:axId val="18096949"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2555,12 +2585,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="51026761"/>
+        <c:crossAx val="85334945"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="42232629"/>
+        <c:axId val="58969142"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2591,7 +2621,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="65201230"/>
+        <c:crossAx val="97377216"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2599,7 +2629,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="65201230"/>
+        <c:axId val="97377216"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2664,7 +2694,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="42232629"/>
+        <c:crossAx val="58969142"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2835,11 +2865,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="76596288"/>
-        <c:axId val="8824960"/>
+        <c:axId val="31722322"/>
+        <c:axId val="14964606"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="76596288"/>
+        <c:axId val="31722322"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2870,7 +2900,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="8824960"/>
+        <c:crossAx val="14964606"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2878,7 +2908,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="8824960"/>
+        <c:axId val="14964606"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2952,7 +2982,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="76596288"/>
+        <c:crossAx val="31722322"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2991,9 +3021,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>196560</xdr:colOff>
+      <xdr:colOff>194760</xdr:colOff>
       <xdr:row>38</xdr:row>
-      <xdr:rowOff>159480</xdr:rowOff>
+      <xdr:rowOff>157680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -3002,7 +3032,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="611640" y="4190040"/>
-        <a:ext cx="6117120" cy="3237120"/>
+        <a:ext cx="6115320" cy="3235320"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -3021,9 +3051,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>379440</xdr:colOff>
+      <xdr:colOff>377640</xdr:colOff>
       <xdr:row>38</xdr:row>
-      <xdr:rowOff>159480</xdr:rowOff>
+      <xdr:rowOff>157680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -3032,7 +3062,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="9069840" y="4190040"/>
-        <a:ext cx="6117120" cy="3237120"/>
+        <a:ext cx="6115320" cy="3235320"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -3051,9 +3081,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>213840</xdr:colOff>
+      <xdr:colOff>212040</xdr:colOff>
       <xdr:row>57</xdr:row>
-      <xdr:rowOff>159480</xdr:rowOff>
+      <xdr:rowOff>157680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -3062,7 +3092,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="611640" y="7809120"/>
-        <a:ext cx="3597120" cy="3237480"/>
+        <a:ext cx="3595320" cy="3235680"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -4276,6 +4306,14 @@
   <mergeCells count="1">
     <mergeCell ref="B2:F2"/>
   </mergeCells>
+  <conditionalFormatting sqref="D6:D17">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>D6="OK"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+      <formula>D6&lt;&gt;"OK"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.25" right="0.25" top="0.4" bottom="0.4" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -5114,6 +5152,14 @@
     <mergeCell ref="E61:J61"/>
     <mergeCell ref="E63:J63"/>
   </mergeCells>
+  <conditionalFormatting sqref="C19">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>ROUND(C19,1)=0</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+      <formula>ROUND(C19,1)&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.25" right="0.25" top="0.4" bottom="0.4" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -7098,6 +7144,14 @@
   <mergeCells count="1">
     <mergeCell ref="B2:F2"/>
   </mergeCells>
+  <conditionalFormatting sqref="E22:J22">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>ROUND(E22,1)=0</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+      <formula>ROUND(E22,1)&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.25" right="0.25" top="0.4" bottom="0.4" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
